--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5782,7 +5782,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>247</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>270</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>276</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>289</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>307</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>343</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>380</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>407</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>447</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>449</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>497</v>
       </c>
@@ -12056,7 +12056,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>514</v>
       </c>
@@ -14096,7 +14096,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>601</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>607</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>616</v>
       </c>
@@ -14706,7 +14706,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>626</v>
       </c>
@@ -15190,7 +15190,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>631</v>
       </c>
@@ -17116,7 +17116,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>665</v>
       </c>
@@ -17360,7 +17360,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>686</v>
       </c>
@@ -17480,7 +17480,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>694</v>
       </c>
@@ -17600,7 +17600,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>703</v>
       </c>
@@ -17722,7 +17722,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>711</v>
       </c>
@@ -18088,7 +18088,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>714</v>
       </c>
@@ -18572,7 +18572,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>720</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>740</v>
       </c>
@@ -20742,7 +20742,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>742</v>
       </c>
@@ -20862,7 +20862,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
         <v>743</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>744</v>
       </c>
@@ -21104,7 +21104,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
         <v>745</v>
       </c>
@@ -21470,7 +21470,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>748</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
         <v>754</v>
       </c>
@@ -23522,7 +23522,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>769</v>
       </c>
@@ -23644,7 +23644,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
         <v>770</v>
       </c>
@@ -24012,12 +24012,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP176">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
